--- a/Companion-Workbooks/Knowledge_Inventory_Workbook.xlsx
+++ b/Companion-Workbooks/Knowledge_Inventory_Workbook.xlsx
@@ -11,11 +11,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WELCOME" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LICENCE" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 1 Supplier Ranking" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 2 Assessment" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 3 Knowledge Inventory" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 4 Transfer Tracker" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 5 Transition" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 17 Supplier Ranking" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 18 Assessment" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 19 Knowledge Inventory" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 20 Transfer Tracker" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form 21 Transition" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXAMPLE A Single-source foundry" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EXAMPLE B Distributor" sheetId="12" state="visible" r:id="rId12"/>
@@ -26,11 +26,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Cover'!$A$1:$I$31</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'WELCOME'!$A$1:$I$70</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'LICENCE'!$A$1:$I$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Form 1 Supplier Ranking'!$A$4:$H$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Form 2 Assessment'!$A$4:$I$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Form 3 Knowledge Inventory'!$A$4:$G$204</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Form 4 Transfer Tracker'!$A$4:$K$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Form 5 Transition'!$A$4:$G$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Form 17 Supplier Ranking'!$A$4:$H$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Form 18 Assessment'!$A$4:$I$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Form 19 Knowledge Inventory'!$A$4:$G$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Form 20 Transfer Tracker'!$A$4:$K$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Form 21 Transition'!$A$4:$G$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'Dashboard'!$A$1:$J$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="H3" s="42" t="inlineStr">
         <is>
-          <t>NF-CW4  ·  v1.0</t>
+          <t>NF-CW4  ·  v2.0</t>
         </is>
       </c>
     </row>
@@ -2236,14 +2236,14 @@
     <row r="11" ht="46" customHeight="1" s="40">
       <c r="B11" s="45" t="inlineStr">
         <is>
-          <t>What Ray Knew</t>
+          <t>The Norwood Files</t>
         </is>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1" s="40">
       <c r="B12" s="46" t="inlineStr">
         <is>
-          <t>A Novel About Organizational Knowledge, Supplier Risk and What Leaves When Somebody Retires</t>
+          <t>A Novel About Risk, Audit and Root Cause in a Factory That Stopped Pretending</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
     <row r="15" ht="26" customHeight="1" s="40">
       <c r="B15" s="47" t="inlineStr">
         <is>
-          <t>Companion to Book Four</t>
+          <t>Companion to Part Four — The Supplier and the Knowledge</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="C21" s="51" t="inlineStr">
         <is>
-          <t>v1.0  ·  NF-CW4</t>
+          <t>v2.0  ·  NF-CW4</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="C23" s="51" t="inlineStr">
         <is>
-          <t>Matches the first edition of the book (Editorial Baseline EBL-3.1)</t>
+          <t>Matches the omnibus first edition of The Norwood Files (build RC-Rev9)</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="C24" s="51" t="inlineStr">
         <is>
-          <t>22 August 2026</t>
+          <t>29 August 2026</t>
         </is>
       </c>
     </row>
@@ -2416,23 +2416,23 @@
     </row>
     <row r="5" ht="21.75" customHeight="1" s="40">
       <c r="A5" s="93">
-        <f>COUNTA('Form 1 Supplier Ranking'!B5:B64)</f>
+        <f>COUNTA('Form 17 Supplier Ranking'!B5:B64)</f>
         <v/>
       </c>
       <c r="C5" s="93">
-        <f>COUNTIF('Form 1 Supplier Ranking'!H5:H64,"CRITICAL*")</f>
+        <f>COUNTIF('Form 17 Supplier Ranking'!H5:H64,"CRITICAL*")</f>
         <v/>
       </c>
       <c r="E5" s="93">
-        <f>COUNTIF('Form 1 Supplier Ranking'!H5:H64,"CERTIFICATE*")</f>
+        <f>COUNTIF('Form 17 Supplier Ranking'!H5:H64,"CERTIFICATE*")</f>
         <v/>
       </c>
       <c r="G5" s="93">
-        <f>COUNTA('Form 3 Knowledge Inventory'!C5:C204)</f>
+        <f>COUNTA('Form 19 Knowledge Inventory'!C5:C204)</f>
         <v/>
       </c>
       <c r="I5" s="93">
-        <f>COUNTIF('Form 4 Transfer Tracker'!K5:K64,"FEWER*")</f>
+        <f>COUNTIF('Form 20 Transfer Tracker'!K5:K64,"FEWER*")</f>
         <v/>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="B48" s="98">
-        <f>COUNTIF('Form 3 Knowledge Inventory'!$D$5:$D$204,"will not transfer")</f>
+        <f>COUNTIF('Form 19 Knowledge Inventory'!$D$5:$D$204,"will not transfer")</f>
         <v/>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="B49" s="98">
-        <f>COUNTIF('Form 3 Knowledge Inventory'!$D$5:$D$204,"apprenticeship")</f>
+        <f>COUNTIF('Form 19 Knowledge Inventory'!$D$5:$D$204,"apprenticeship")</f>
         <v/>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="B50" s="98">
-        <f>COUNTIF('Form 3 Knowledge Inventory'!$D$5:$D$204,"to be engineered out")</f>
+        <f>COUNTIF('Form 19 Knowledge Inventory'!$D$5:$D$204,"to be engineered out")</f>
         <v/>
       </c>
     </row>
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="B51" s="98">
-        <f>COUNTIF('Form 3 Knowledge Inventory'!$D$5:$D$204,"to be documented")</f>
+        <f>COUNTIF('Form 19 Knowledge Inventory'!$D$5:$D$204,"to be documented")</f>
         <v/>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="B52" s="98">
-        <f>COUNTIF('Form 3 Knowledge Inventory'!$D$5:$D$204,"already documented")</f>
+        <f>COUNTIF('Form 19 Knowledge Inventory'!$D$5:$D$204,"already documented")</f>
         <v/>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="B55" s="98">
-        <f>COUNTIF('Form 1 Supplier Ranking'!$E$5:$E$64,"indefinitely")</f>
+        <f>COUNTIF('Form 17 Supplier Ranking'!$E$5:$E$64,"indefinitely")</f>
         <v/>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="B56" s="98">
-        <f>COUNTIF('Form 1 Supplier Ranking'!$E$5:$E$64,"over a year")</f>
+        <f>COUNTIF('Form 17 Supplier Ranking'!$E$5:$E$64,"over a year")</f>
         <v/>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
         </is>
       </c>
       <c r="B57" s="98">
-        <f>COUNTIF('Form 1 Supplier Ranking'!$E$5:$E$64,"3-12 months")</f>
+        <f>COUNTIF('Form 17 Supplier Ranking'!$E$5:$E$64,"3-12 months")</f>
         <v/>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="B58" s="98">
-        <f>COUNTIF('Form 1 Supplier Ranking'!$E$5:$E$64,"1-3 months")</f>
+        <f>COUNTIF('Form 17 Supplier Ranking'!$E$5:$E$64,"1-3 months")</f>
         <v/>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="B59" s="98">
-        <f>COUNTIF('Form 1 Supplier Ranking'!$E$5:$E$64,"2-4 weeks")</f>
+        <f>COUNTIF('Form 17 Supplier Ranking'!$E$5:$E$64,"2-4 weeks")</f>
         <v/>
       </c>
     </row>
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="B60" s="98">
-        <f>COUNTIF('Form 1 Supplier Ranking'!$E$5:$E$64,"days")</f>
+        <f>COUNTIF('Form 17 Supplier Ranking'!$E$5:$E$64,"days")</f>
         <v/>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="B63" s="98">
-        <f>COUNTIF('Form 5 Transition'!$C$5:$C$44,"already done")</f>
+        <f>COUNTIF('Form 21 Transition'!$C$5:$C$44,"already done")</f>
         <v/>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="B64" s="98">
-        <f>COUNTIF('Form 5 Transition'!$C$5:$C$44,"done not evidenced")</f>
+        <f>COUNTIF('Form 21 Transition'!$C$5:$C$44,"done not evidenced")</f>
         <v/>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="B65" s="98">
-        <f>COUNTIF('Form 5 Transition'!$C$5:$C$44,"not done low effort")</f>
+        <f>COUNTIF('Form 21 Transition'!$C$5:$C$44,"not done low effort")</f>
         <v/>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="B66" s="98">
-        <f>COUNTIF('Form 5 Transition'!$C$5:$C$44,"not done real work")</f>
+        <f>COUNTIF('Form 21 Transition'!$C$5:$C$44,"not done real work")</f>
         <v/>
       </c>
     </row>
@@ -2745,7 +2745,7 @@
   <pageSetup orientation="landscape" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW4 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Four&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Four&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2779,7 +2779,7 @@
     <row r="2" ht="15.75" customHeight="1" s="40">
       <c r="A2" s="72" t="inlineStr">
         <is>
-          <t>Worked assessment from Part 2 of the book. Read, do not edit.</t>
+          <t>Worked assessment from Part Four of the book. Read, do not edit.</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW4 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Four&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Four&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2949,7 +2949,7 @@
     <row r="2" ht="15.75" customHeight="1" s="40">
       <c r="A2" s="72" t="inlineStr">
         <is>
-          <t>Worked assessment from Part 2 of the book. Read, do not edit.</t>
+          <t>Worked assessment from Part Four of the book. Read, do not edit.</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW4 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Four&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Four&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3095,7 +3095,7 @@
     <row r="2" ht="15.75" customHeight="1" s="40">
       <c r="A2" s="72" t="inlineStr">
         <is>
-          <t>Worked assessment from Part 2 of the book. Read, do not edit.</t>
+          <t>Worked assessment from Part Four of the book. Read, do not edit.</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW4 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Four&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Four&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3246,7 +3246,7 @@
     <row r="7" ht="15" customHeight="1" s="40">
       <c r="B7" s="105" t="inlineStr">
         <is>
-          <t>Companion to Book Four</t>
+          <t>Companion to Part Four</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
     <row r="9" ht="15" customHeight="1" s="40">
       <c r="B9" s="106" t="inlineStr">
         <is>
-          <t>Document code: NF-CW4 · Identity: NBSM v1.0 · Baseline: EBL-3.1 · Issued 22 August 2026</t>
+          <t>Document code: NF-CW4 · Identity: NBSM v1.0 · Baseline: RC-Rev9 · Issued 29 August 2026</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="H2" s="42" t="inlineStr">
         <is>
-          <t>NF-CW4  ·  v1.0</t>
+          <t>NF-CW4  ·  v2.0</t>
         </is>
       </c>
     </row>
@@ -3365,7 +3365,7 @@
     <row r="8" ht="14" customHeight="1" s="40">
       <c r="B8" s="55" t="inlineStr">
         <is>
-          <t>This workbook is the working half of Book Four of The Norwood Files. It carries the forms from the book with the rules already written into the formulas, so that the method can be run on a real process instead of read about. Its subject is supplier risk ranked by consequence rather than spend, and the knowledge that leaves when a person does: elicitation, transfer and verification.</t>
+          <t>This workbook is the working half of Part Four of The Norwood Files. It carries the forms from the book with the rules already written into the formulas, so that the method can be run on a real process instead of read about. Its subject is supplier risk ranked by consequence rather than spend, and the knowledge that leaves when a person does: elicitation, transfer and verification.</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
     <row r="21" ht="14" customHeight="1" s="40">
       <c r="B21" s="55" t="inlineStr">
         <is>
-          <t>The numbered sheets carry the same Form numbers as the book. Form 3 in the book is Form 3 in this file. The sheets prefixed EXAMPLE are the worked cases from the book, complete and populated, so that you can see how a row behaves before you clear it and start on your own process.</t>
+          <t>The numbered sheets carry the same Form numbers as the book. Form 19 in the book is Form 19 in this file. The sheets prefixed EXAMPLE are the worked cases from the book, complete and populated, so that you can see how a row behaves before you clear it and start on your own process.</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
     <row r="42" ht="28" customHeight="1" s="40">
       <c r="B42" s="59" t="inlineStr">
         <is>
-          <t>Form 1 Supplier Ranking</t>
+          <t>Form 17 Supplier Ranking</t>
         </is>
       </c>
       <c r="C42" s="60" t="inlineStr">
@@ -3540,7 +3540,7 @@
     <row r="43" ht="28" customHeight="1" s="40">
       <c r="B43" s="59" t="inlineStr">
         <is>
-          <t>Form 2 Assessment</t>
+          <t>Form 18 Assessment</t>
         </is>
       </c>
       <c r="C43" s="60" t="inlineStr">
@@ -3557,7 +3557,7 @@
     <row r="44" ht="39.5" customHeight="1" s="40">
       <c r="B44" s="59" t="inlineStr">
         <is>
-          <t>Form 3 Knowledge Inventory</t>
+          <t>Form 19 Knowledge Inventory</t>
         </is>
       </c>
       <c r="C44" s="60" t="inlineStr">
@@ -3574,7 +3574,7 @@
     <row r="45" ht="28" customHeight="1" s="40">
       <c r="B45" s="59" t="inlineStr">
         <is>
-          <t>Form 4 Transfer Tracker</t>
+          <t>Form 20 Transfer Tracker</t>
         </is>
       </c>
       <c r="C45" s="60" t="inlineStr">
@@ -3591,7 +3591,7 @@
     <row r="46" ht="28" customHeight="1" s="40">
       <c r="B46" s="59" t="inlineStr">
         <is>
-          <t>Form 5 Transition</t>
+          <t>Form 21 Transition</t>
         </is>
       </c>
       <c r="C46" s="60" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="H2" s="42" t="inlineStr">
         <is>
-          <t>NF-CW4  ·  v1.0</t>
+          <t>NF-CW4  ·  v2.0</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3877,7 @@
       <c r="C9" s="49" t="n"/>
       <c r="D9" s="67" t="inlineStr">
         <is>
-          <t>The Norwood Files — Companion to Book Four</t>
+          <t>The Norwood Files — Companion to Part Four</t>
         </is>
       </c>
       <c r="E9" s="49" t="n"/>
@@ -3894,7 +3894,7 @@
       <c r="C10" s="49" t="n"/>
       <c r="D10" s="67" t="inlineStr">
         <is>
-          <t>What Ray Knew</t>
+          <t>The Norwood Files</t>
         </is>
       </c>
       <c r="E10" s="49" t="n"/>
@@ -3928,7 +3928,7 @@
       <c r="C12" s="49" t="n"/>
       <c r="D12" s="67" t="inlineStr">
         <is>
-          <t>v1.0</t>
+          <t>v2.0</t>
         </is>
       </c>
       <c r="E12" s="49" t="n"/>
@@ -3945,7 +3945,7 @@
       <c r="C13" s="49" t="n"/>
       <c r="D13" s="67" t="inlineStr">
         <is>
-          <t>v1.0  ·  issued 22 August 2026</t>
+          <t>v2.0  ·  issued 29 August 2026</t>
         </is>
       </c>
       <c r="E13" s="49" t="n"/>
@@ -3979,7 +3979,7 @@
       <c r="C15" s="49" t="n"/>
       <c r="D15" s="67" t="inlineStr">
         <is>
-          <t>EBL-3.1</t>
+          <t>RC-Rev9</t>
         </is>
       </c>
       <c r="E15" s="49" t="n"/>
@@ -4053,7 +4053,7 @@
     <row r="27" ht="13" customHeight="1" s="40">
       <c r="B27" s="68" t="inlineStr">
         <is>
-          <t>This workbook accompanies What Ray Knew and is supplied free of charge with the book. You may use it, adapt it and reproduce it inside your own organization for your own quality management system.</t>
+          <t>This workbook accompanies The Norwood Files and is supplied free of charge with the book. You may use it, adapt it and reproduce it inside your own organization for your own quality management system.</t>
         </is>
       </c>
     </row>
@@ -4154,14 +4154,14 @@
     <row r="1" ht="25.5" customHeight="1" s="40">
       <c r="A1" s="71" t="inlineStr">
         <is>
-          <t>WHAT RAY KNEW—COMPANION WORKBOOK</t>
+          <t>THE NORWOOD FILES — PART FOUR COMPANION</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1" s="40">
       <c r="A2" s="72" t="inlineStr">
         <is>
-          <t>The forms from Part 3. Free, no sign-up. Everything here is also printed in the book.</t>
+          <t>The forms from Part Five. Free, no sign-up. Everything here is also printed in the book.</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
     <row r="5" ht="39" customHeight="1" s="40">
       <c r="B5" s="74" t="inlineStr">
         <is>
-          <t>The supplier consequence ranking, assessment record, knowledge inventory, transfer verification tracker and transition gap analysis from Part 3, plus the three worked assessments from Part 2.</t>
+          <t>The supplier consequence ranking, assessment record, knowledge inventory, transfer verification tracker and transition gap analysis from Part Five, plus the three worked assessments from Part Four.</t>
         </is>
       </c>
     </row>
@@ -4197,35 +4197,35 @@
     <row r="8" ht="39" customHeight="1" s="40">
       <c r="B8" s="74" t="inlineStr">
         <is>
-          <t>1.  Fill 'Form 1 Supplier Ranking' first, and fill the consequence column before you look at the spend column. The order will not resemble your spend ranking. This is the only part of this file that changes what you do next week.</t>
+          <t>1.  Fill 'Form 17 Supplier Ranking' first, and fill the consequence column before you look at the spend column. The order will not resemble your spend ranking. This is the only part of this file that changes what you do next week.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="25.5" customHeight="1" s="40">
       <c r="B9" s="74" t="inlineStr">
         <is>
-          <t>2.  Assess the top of that list on 'Form 2 Assessment'. Both percentages are mandatory fields—the sheet flags a row where either is missing.</t>
+          <t>2.  Assess the top of that list on 'Form 18 Assessment'. Both percentages are mandatory fields—the sheet flags a row where either is missing.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="25.5" customHeight="1" s="40">
       <c r="B10" s="74" t="inlineStr">
         <is>
-          <t>3.  'Form 3 Knowledge Inventory' is one row per PERSON, not per role, and is filled in for everybody experienced rather than only for whoever is leaving.</t>
+          <t>3.  'Form 19 Knowledge Inventory' is one row per PERSON, not per role, and is filled in for everybody experienced rather than only for whoever is leaving.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="25.5" customHeight="1" s="40">
       <c r="B11" s="74" t="inlineStr">
         <is>
-          <t>4.  'Form 4 Transfer Tracker' takes how often the difficult event happens and the leaving date, and tells you how many chances you have. Under three, it turns red.</t>
+          <t>4.  'Form 20 Transfer Tracker' takes how often the difficult event happens and the leaving date, and tells you how many chances you have. Under three, it turns red.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="25.5" customHeight="1" s="40">
       <c r="B12" s="74" t="inlineStr">
         <is>
-          <t>5.  'Form 5 Transition' has four verdicts and nothing else. If it will not fit on two printed pages you are writing a document rather than doing an analysis.</t>
+          <t>5.  'Form 21 Transition' has four verdicts and nothing else. If it will not fit on two printed pages you are writing a document rather than doing an analysis.</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4267,7 @@
     <row r="18" ht="39" customHeight="1" s="40">
       <c r="B18" s="74" t="inlineStr">
         <is>
-          <t>The three sheets prefixed EXAMPLE are the worked assessments from Part 2. Two of them end in a risk the plant decided to keep, which is the ordinary outcome of an honest assessment and almost never the outcome of a published one.</t>
+          <t>The three sheets prefixed EXAMPLE are the worked assessments from Part Four. Two of them end in a risk the plant decided to keep, which is the ordinary outcome of an honest assessment and almost never the outcome of a published one.</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
     <row r="22" ht="15" customHeight="1" s="40">
       <c r="A22" s="75" t="inlineStr">
         <is>
-          <t>The Norwood Files · Companion to Book Four · v1.0 · issued 22 August 2026 · matches the first edition (Editorial Baseline EBL-3.1)</t>
+          <t>The Norwood Files · Companion to Part Four · v2.0 · issued 29 August 2026 · matches the omnibus first edition (build RC-Rev9)</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4304,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW4 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Four&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Four&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5215,7 +5215,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW4 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Four&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Four&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -6174,7 +6174,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW4 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Four&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Four&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -8709,7 +8709,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW4 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Four&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Four&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -9997,7 +9997,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW4 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Four&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Four&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -10595,7 +10595,7 @@
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentOddEven="0" differentFirst="0">
     <oddHeader>&amp;L&amp;8 THE NORWOOD FILES  ·  ■&amp;R&amp;8 NF-CW4 · NBSM v1.0</oddHeader>
-    <oddFooter>&amp;L&amp;8 Companion to Book Four&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
+    <oddFooter>&amp;L&amp;8 Companion to Part Four&amp;C&amp;8 Page &amp;P of &amp;N&amp;R&amp;8 &amp;D</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/Companion-Workbooks/Knowledge_Inventory_Workbook.xlsx
+++ b/Companion-Workbooks/Knowledge_Inventory_Workbook.xlsx
@@ -4144,7 +4144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="70" min="1" max="1"/>
@@ -4285,9 +4285,30 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22" ht="15" customHeight="1" s="40">
-      <c r="A22" s="75" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="40">
+      <c r="A21" s="73" t="inlineStr">
+        <is>
+          <t>THE SILENT EXPIRY WEBSITE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="39" customHeight="1" s="40">
+      <c r="B22" s="74" t="inlineStr">
+        <is>
+          <t>Explore the complete framework: the canonical definition of Silent Expiry, the documented evidence behind it, and a fifty-two article curriculum. Free to read, nothing to sign up for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="55">
+      <c r="B23" s="74" t="inlineStr">
+        <is>
+          <t>https://silent-expiry.pages.dev/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25" ht="15" customHeight="1" s="40">
+      <c r="A25" s="75" t="inlineStr">
         <is>
           <t>The Norwood Files · Companion to Part Four · v2.0 · issued 29 August 2026 · matches the omnibus first edition (build RC-Rev9)</t>
         </is>
